--- a/fil-c-x64/Running erasure.xlsx
+++ b/fil-c-x64/Running erasure.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>86.4451</v>
+        <v>86.12</v>
       </c>
       <c r="C2" t="n">
-        <v>124.729</v>
+        <v>124.102</v>
       </c>
       <c r="D2" t="n">
-        <v>49.5287</v>
+        <v>49.8917</v>
       </c>
       <c r="E2" t="n">
-        <v>22.8676</v>
+        <v>22.9466</v>
       </c>
       <c r="F2" t="n">
-        <v>39.4053</v>
+        <v>39.9453</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>86.59310000000001</v>
+        <v>85.9213</v>
       </c>
       <c r="C3" t="n">
-        <v>123.296</v>
+        <v>123.307</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2526</v>
+        <v>50.0425</v>
       </c>
       <c r="E3" t="n">
-        <v>22.2117</v>
+        <v>22.263</v>
       </c>
       <c r="F3" t="n">
-        <v>39.2941</v>
+        <v>39.7002</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>85.2226</v>
+        <v>85.10899999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>123.148</v>
+        <v>123.379</v>
       </c>
       <c r="D4" t="n">
-        <v>49.8111</v>
+        <v>50.1648</v>
       </c>
       <c r="E4" t="n">
-        <v>21.7162</v>
+        <v>21.8267</v>
       </c>
       <c r="F4" t="n">
-        <v>38.5165</v>
+        <v>39.0735</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>84.1682</v>
+        <v>84.32470000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>121.823</v>
+        <v>122.04</v>
       </c>
       <c r="D5" t="n">
-        <v>50.1189</v>
+        <v>50.2534</v>
       </c>
       <c r="E5" t="n">
-        <v>21.4631</v>
+        <v>21.5042</v>
       </c>
       <c r="F5" t="n">
-        <v>38.6517</v>
+        <v>38.5931</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>84.3837</v>
+        <v>84.3329</v>
       </c>
       <c r="C6" t="n">
-        <v>121.741</v>
+        <v>120.997</v>
       </c>
       <c r="D6" t="n">
-        <v>49.9484</v>
+        <v>49.859</v>
       </c>
       <c r="E6" t="n">
-        <v>21.1492</v>
+        <v>21.12</v>
       </c>
       <c r="F6" t="n">
-        <v>38.0793</v>
+        <v>38.4987</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>83.9453</v>
+        <v>83.7564</v>
       </c>
       <c r="C7" t="n">
-        <v>120.537</v>
+        <v>121.078</v>
       </c>
       <c r="D7" t="n">
-        <v>51.0683</v>
+        <v>50.4503</v>
       </c>
       <c r="E7" t="n">
-        <v>20.6549</v>
+        <v>20.5884</v>
       </c>
       <c r="F7" t="n">
-        <v>37.432</v>
+        <v>37.3038</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>83.1002</v>
+        <v>82.8734</v>
       </c>
       <c r="C8" t="n">
-        <v>119.921</v>
+        <v>119.637</v>
       </c>
       <c r="D8" t="n">
-        <v>51.0465</v>
+        <v>51.2239</v>
       </c>
       <c r="E8" t="n">
-        <v>20.2229</v>
+        <v>20.2455</v>
       </c>
       <c r="F8" t="n">
-        <v>36.9766</v>
+        <v>37.2192</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>82.1091</v>
+        <v>82.1345</v>
       </c>
       <c r="C9" t="n">
-        <v>118.649</v>
+        <v>119.402</v>
       </c>
       <c r="D9" t="n">
-        <v>51.9071</v>
+        <v>51.6083</v>
       </c>
       <c r="E9" t="n">
-        <v>27.0053</v>
+        <v>27.0806</v>
       </c>
       <c r="F9" t="n">
-        <v>44.4026</v>
+        <v>44.5572</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>89.8073</v>
+        <v>89.69450000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>127.014</v>
+        <v>126.914</v>
       </c>
       <c r="D10" t="n">
-        <v>51.1075</v>
+        <v>50.2434</v>
       </c>
       <c r="E10" t="n">
-        <v>26.3377</v>
+        <v>26.7567</v>
       </c>
       <c r="F10" t="n">
-        <v>43.8081</v>
+        <v>43.4878</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>89.9851</v>
+        <v>89.70610000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>126.999</v>
+        <v>125.915</v>
       </c>
       <c r="D11" t="n">
-        <v>51.5923</v>
+        <v>51.6498</v>
       </c>
       <c r="E11" t="n">
-        <v>26.1386</v>
+        <v>26.0203</v>
       </c>
       <c r="F11" t="n">
-        <v>43.59</v>
+        <v>43.1463</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>89.5376</v>
+        <v>89.37</v>
       </c>
       <c r="C12" t="n">
-        <v>125.019</v>
+        <v>123.837</v>
       </c>
       <c r="D12" t="n">
-        <v>52.767</v>
+        <v>52.4883</v>
       </c>
       <c r="E12" t="n">
-        <v>25.2945</v>
+        <v>25.9805</v>
       </c>
       <c r="F12" t="n">
-        <v>43.0519</v>
+        <v>43.4165</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>88.6392</v>
+        <v>88.36239999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>125.802</v>
+        <v>125.882</v>
       </c>
       <c r="D13" t="n">
-        <v>51.0993</v>
+        <v>51.829</v>
       </c>
       <c r="E13" t="n">
-        <v>25.06</v>
+        <v>24.8882</v>
       </c>
       <c r="F13" t="n">
-        <v>42.2326</v>
+        <v>41.7793</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>88.18389999999999</v>
+        <v>88.1002</v>
       </c>
       <c r="C14" t="n">
-        <v>126.088</v>
+        <v>123.925</v>
       </c>
       <c r="D14" t="n">
-        <v>51.023</v>
+        <v>50.3834</v>
       </c>
       <c r="E14" t="n">
-        <v>24.7036</v>
+        <v>24.646</v>
       </c>
       <c r="F14" t="n">
-        <v>41.6305</v>
+        <v>41.5642</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>87.8976</v>
+        <v>87.4419</v>
       </c>
       <c r="C15" t="n">
-        <v>122.413</v>
+        <v>121.793</v>
       </c>
       <c r="D15" t="n">
-        <v>52.3791</v>
+        <v>51.659</v>
       </c>
       <c r="E15" t="n">
-        <v>24.2014</v>
+        <v>24.1212</v>
       </c>
       <c r="F15" t="n">
-        <v>41.3296</v>
+        <v>41.3822</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>87.1769</v>
+        <v>86.8741</v>
       </c>
       <c r="C16" t="n">
-        <v>122.828</v>
+        <v>124.293</v>
       </c>
       <c r="D16" t="n">
-        <v>52.4619</v>
+        <v>52.3496</v>
       </c>
       <c r="E16" t="n">
-        <v>24.0877</v>
+        <v>23.9741</v>
       </c>
       <c r="F16" t="n">
-        <v>41.5404</v>
+        <v>41.7639</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>86.6583</v>
+        <v>86.3672</v>
       </c>
       <c r="C17" t="n">
-        <v>123.999</v>
+        <v>122.202</v>
       </c>
       <c r="D17" t="n">
-        <v>52.0389</v>
+        <v>51.0196</v>
       </c>
       <c r="E17" t="n">
-        <v>23.5856</v>
+        <v>23.3297</v>
       </c>
       <c r="F17" t="n">
-        <v>40.9023</v>
+        <v>40.925</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>85.6354</v>
+        <v>85.33710000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>123.246</v>
+        <v>122.817</v>
       </c>
       <c r="D18" t="n">
-        <v>52.4958</v>
+        <v>52.4439</v>
       </c>
       <c r="E18" t="n">
-        <v>22.9833</v>
+        <v>22.9784</v>
       </c>
       <c r="F18" t="n">
-        <v>39.8422</v>
+        <v>39.6015</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>85.5213</v>
+        <v>85.1142</v>
       </c>
       <c r="C19" t="n">
-        <v>121.119</v>
+        <v>119.677</v>
       </c>
       <c r="D19" t="n">
-        <v>52.5238</v>
+        <v>51.4348</v>
       </c>
       <c r="E19" t="n">
-        <v>22.382</v>
+        <v>22.3806</v>
       </c>
       <c r="F19" t="n">
-        <v>39.9739</v>
+        <v>39.6856</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>84.6418</v>
+        <v>84.43600000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>121.539</v>
+        <v>122.681</v>
       </c>
       <c r="D20" t="n">
-        <v>52.492</v>
+        <v>52.2235</v>
       </c>
       <c r="E20" t="n">
-        <v>22.3749</v>
+        <v>21.8709</v>
       </c>
       <c r="F20" t="n">
-        <v>39.6057</v>
+        <v>39.6214</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>84.0839</v>
+        <v>83.7739</v>
       </c>
       <c r="C21" t="n">
-        <v>121.726</v>
+        <v>121.489</v>
       </c>
       <c r="D21" t="n">
-        <v>55.007</v>
+        <v>55.1306</v>
       </c>
       <c r="E21" t="n">
-        <v>21.5406</v>
+        <v>21.4901</v>
       </c>
       <c r="F21" t="n">
-        <v>38.4342</v>
+        <v>38.5424</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>83.3141</v>
+        <v>82.92489999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>120.767</v>
+        <v>119.007</v>
       </c>
       <c r="D22" t="n">
-        <v>55.5838</v>
+        <v>54.9051</v>
       </c>
       <c r="E22" t="n">
-        <v>20.9763</v>
+        <v>20.924</v>
       </c>
       <c r="F22" t="n">
-        <v>38.1593</v>
+        <v>38.7751</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>82.4893</v>
+        <v>82.21769999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>118.784</v>
+        <v>118.481</v>
       </c>
       <c r="D23" t="n">
-        <v>53.3908</v>
+        <v>54.0827</v>
       </c>
       <c r="E23" t="n">
-        <v>27.371</v>
+        <v>27.6116</v>
       </c>
       <c r="F23" t="n">
-        <v>45.0289</v>
+        <v>45.6386</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>90.3867</v>
+        <v>90.0829</v>
       </c>
       <c r="C24" t="n">
-        <v>127.442</v>
+        <v>126.177</v>
       </c>
       <c r="D24" t="n">
-        <v>54.8671</v>
+        <v>53.6715</v>
       </c>
       <c r="E24" t="n">
-        <v>26.759</v>
+        <v>26.8533</v>
       </c>
       <c r="F24" t="n">
-        <v>43.7196</v>
+        <v>43.6594</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>90.029</v>
+        <v>89.6135</v>
       </c>
       <c r="C25" t="n">
-        <v>128.149</v>
+        <v>126.581</v>
       </c>
       <c r="D25" t="n">
-        <v>55.1534</v>
+        <v>54.9761</v>
       </c>
       <c r="E25" t="n">
-        <v>26.419</v>
+        <v>26.3169</v>
       </c>
       <c r="F25" t="n">
-        <v>44.8894</v>
+        <v>44.902</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>89.2808</v>
+        <v>89.173</v>
       </c>
       <c r="C26" t="n">
-        <v>126.873</v>
+        <v>127.649</v>
       </c>
       <c r="D26" t="n">
-        <v>55.1371</v>
+        <v>55.3707</v>
       </c>
       <c r="E26" t="n">
-        <v>25.8948</v>
+        <v>25.6454</v>
       </c>
       <c r="F26" t="n">
-        <v>43.9947</v>
+        <v>44.5339</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>89.0492</v>
+        <v>89.0685</v>
       </c>
       <c r="C27" t="n">
-        <v>126.608</v>
+        <v>127.441</v>
       </c>
       <c r="D27" t="n">
-        <v>56.3471</v>
+        <v>55.5376</v>
       </c>
       <c r="E27" t="n">
-        <v>25.4809</v>
+        <v>25.4564</v>
       </c>
       <c r="F27" t="n">
-        <v>43.6189</v>
+        <v>43.6628</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>88.4023</v>
+        <v>88.1092</v>
       </c>
       <c r="C28" t="n">
-        <v>126.188</v>
+        <v>125.391</v>
       </c>
       <c r="D28" t="n">
-        <v>52.2337</v>
+        <v>55.186</v>
       </c>
       <c r="E28" t="n">
-        <v>24.9122</v>
+        <v>24.977</v>
       </c>
       <c r="F28" t="n">
-        <v>41.7953</v>
+        <v>42.4108</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>87.9542</v>
+        <v>87.636</v>
       </c>
       <c r="C29" t="n">
-        <v>125.146</v>
+        <v>125.441</v>
       </c>
       <c r="D29" t="n">
-        <v>55.3393</v>
+        <v>55.0265</v>
       </c>
       <c r="E29" t="n">
-        <v>24.5177</v>
+        <v>24.5991</v>
       </c>
       <c r="F29" t="n">
-        <v>43.4117</v>
+        <v>43.2992</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>87.0408</v>
+        <v>86.8558</v>
       </c>
       <c r="C30" t="n">
-        <v>124.48</v>
+        <v>125.135</v>
       </c>
       <c r="D30" t="n">
-        <v>57.3512</v>
+        <v>56.4521</v>
       </c>
       <c r="E30" t="n">
-        <v>24.0098</v>
+        <v>23.8491</v>
       </c>
       <c r="F30" t="n">
-        <v>41.0724</v>
+        <v>41.7032</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>86.33799999999999</v>
+        <v>86.2685</v>
       </c>
       <c r="C31" t="n">
-        <v>124.044</v>
+        <v>126.334</v>
       </c>
       <c r="D31" t="n">
-        <v>55.7383</v>
+        <v>55.1754</v>
       </c>
       <c r="E31" t="n">
-        <v>23.5424</v>
+        <v>23.4554</v>
       </c>
       <c r="F31" t="n">
-        <v>42.1275</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>86.1536</v>
+        <v>86.0017</v>
       </c>
       <c r="C32" t="n">
-        <v>123.544</v>
+        <v>123.226</v>
       </c>
       <c r="D32" t="n">
-        <v>56.5413</v>
+        <v>55.0009</v>
       </c>
       <c r="E32" t="n">
-        <v>23.2356</v>
+        <v>23.1587</v>
       </c>
       <c r="F32" t="n">
-        <v>40.1568</v>
+        <v>41.1535</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>85.66030000000001</v>
+        <v>85.2761</v>
       </c>
       <c r="C33" t="n">
-        <v>125.642</v>
+        <v>124.618</v>
       </c>
       <c r="D33" t="n">
-        <v>55.4948</v>
+        <v>55.827</v>
       </c>
       <c r="E33" t="n">
-        <v>22.6798</v>
+        <v>22.6671</v>
       </c>
       <c r="F33" t="n">
-        <v>40.3544</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>84.94459999999999</v>
+        <v>85.20489999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>123.72</v>
+        <v>125.274</v>
       </c>
       <c r="D34" t="n">
-        <v>57.5559</v>
+        <v>57.5284</v>
       </c>
       <c r="E34" t="n">
-        <v>22.2421</v>
+        <v>22.2482</v>
       </c>
       <c r="F34" t="n">
-        <v>41.4854</v>
+        <v>40.7213</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>84.2794</v>
+        <v>83.852</v>
       </c>
       <c r="C35" t="n">
-        <v>125.124</v>
+        <v>124.619</v>
       </c>
       <c r="D35" t="n">
-        <v>61.9436</v>
+        <v>60.01</v>
       </c>
       <c r="E35" t="n">
-        <v>21.7705</v>
+        <v>21.7481</v>
       </c>
       <c r="F35" t="n">
-        <v>41.4389</v>
+        <v>41.2354</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>83.5732</v>
+        <v>83.3374</v>
       </c>
       <c r="C36" t="n">
-        <v>122.84</v>
+        <v>123.126</v>
       </c>
       <c r="D36" t="n">
-        <v>61.4872</v>
+        <v>61.317</v>
       </c>
       <c r="E36" t="n">
-        <v>21.3076</v>
+        <v>21.2876</v>
       </c>
       <c r="F36" t="n">
-        <v>39.1588</v>
+        <v>38.585</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>82.7957</v>
+        <v>82.57980000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>118.88</v>
+        <v>122.007</v>
       </c>
       <c r="D37" t="n">
-        <v>61.4097</v>
+        <v>60.6669</v>
       </c>
       <c r="E37" t="n">
-        <v>27.4852</v>
+        <v>27.4659</v>
       </c>
       <c r="F37" t="n">
-        <v>49.4803</v>
+        <v>44.911</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>90.1216</v>
+        <v>89.87990000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>128.395</v>
+        <v>128.514</v>
       </c>
       <c r="D38" t="n">
-        <v>62.3781</v>
+        <v>60.4703</v>
       </c>
       <c r="E38" t="n">
-        <v>27.0055</v>
+        <v>27.0244</v>
       </c>
       <c r="F38" t="n">
-        <v>44.7948</v>
+        <v>44.4969</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>89.9639</v>
+        <v>89.8331</v>
       </c>
       <c r="C39" t="n">
-        <v>128.928</v>
+        <v>126.829</v>
       </c>
       <c r="D39" t="n">
-        <v>60.0624</v>
+        <v>60.1079</v>
       </c>
       <c r="E39" t="n">
-        <v>26.4479</v>
+        <v>26.6892</v>
       </c>
       <c r="F39" t="n">
-        <v>44.3881</v>
+        <v>44.8669</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>89.5074</v>
+        <v>89.3827</v>
       </c>
       <c r="C40" t="n">
-        <v>134.951</v>
+        <v>123.097</v>
       </c>
       <c r="D40" t="n">
-        <v>61.0518</v>
+        <v>61.8134</v>
       </c>
       <c r="E40" t="n">
-        <v>25.9293</v>
+        <v>25.5247</v>
       </c>
       <c r="F40" t="n">
-        <v>43.3978</v>
+        <v>42.9888</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>88.78579999999999</v>
+        <v>88.4748</v>
       </c>
       <c r="C41" t="n">
-        <v>127.747</v>
+        <v>130.278</v>
       </c>
       <c r="D41" t="n">
-        <v>61.9046</v>
+        <v>59.0128</v>
       </c>
       <c r="E41" t="n">
-        <v>25.371</v>
+        <v>25.676</v>
       </c>
       <c r="F41" t="n">
-        <v>43.0058</v>
+        <v>43.1651</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>88.54949999999999</v>
+        <v>88.3732</v>
       </c>
       <c r="C42" t="n">
-        <v>126.947</v>
+        <v>128.513</v>
       </c>
       <c r="D42" t="n">
-        <v>59.8995</v>
+        <v>59.244</v>
       </c>
       <c r="E42" t="n">
-        <v>25.1034</v>
+        <v>25.0938</v>
       </c>
       <c r="F42" t="n">
-        <v>42.2677</v>
+        <v>42.0381</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>87.9547</v>
+        <v>87.8496</v>
       </c>
       <c r="C43" t="n">
-        <v>127.416</v>
+        <v>128.679</v>
       </c>
       <c r="D43" t="n">
-        <v>65.3437</v>
+        <v>61.8403</v>
       </c>
       <c r="E43" t="n">
-        <v>24.6774</v>
+        <v>24.6131</v>
       </c>
       <c r="F43" t="n">
-        <v>43.0406</v>
+        <v>42.1341</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>87.069</v>
+        <v>86.9902</v>
       </c>
       <c r="C44" t="n">
-        <v>127.622</v>
+        <v>129.756</v>
       </c>
       <c r="D44" t="n">
-        <v>61.29</v>
+        <v>61.1514</v>
       </c>
       <c r="E44" t="n">
-        <v>24.2534</v>
+        <v>24.1316</v>
       </c>
       <c r="F44" t="n">
-        <v>42.6011</v>
+        <v>43.6484</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>86.7441</v>
+        <v>86.5963</v>
       </c>
       <c r="C45" t="n">
-        <v>130.324</v>
+        <v>128.874</v>
       </c>
       <c r="D45" t="n">
-        <v>60.5607</v>
+        <v>59.454</v>
       </c>
       <c r="E45" t="n">
-        <v>23.788</v>
+        <v>24.1942</v>
       </c>
       <c r="F45" t="n">
-        <v>40.7226</v>
+        <v>40.8262</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>86.21769999999999</v>
+        <v>86.11799999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>129.238</v>
+        <v>127.899</v>
       </c>
       <c r="D46" t="n">
-        <v>65.30289999999999</v>
+        <v>66.72410000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>23.2617</v>
+        <v>23.2757</v>
       </c>
       <c r="F46" t="n">
-        <v>41.5883</v>
+        <v>40.355</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>85.5774</v>
+        <v>85.3776</v>
       </c>
       <c r="C47" t="n">
-        <v>125.56</v>
+        <v>124.79</v>
       </c>
       <c r="D47" t="n">
-        <v>63.0092</v>
+        <v>63.645</v>
       </c>
       <c r="E47" t="n">
-        <v>22.8591</v>
+        <v>22.8589</v>
       </c>
       <c r="F47" t="n">
-        <v>41.1374</v>
+        <v>43.6403</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>84.5215</v>
+        <v>84.6033</v>
       </c>
       <c r="C48" t="n">
-        <v>131.665</v>
+        <v>130.45</v>
       </c>
       <c r="D48" t="n">
-        <v>60.4321</v>
+        <v>62.6094</v>
       </c>
       <c r="E48" t="n">
-        <v>22.3182</v>
+        <v>22.3128</v>
       </c>
       <c r="F48" t="n">
-        <v>42.8778</v>
+        <v>39.4845</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>84.181</v>
+        <v>84.1027</v>
       </c>
       <c r="C49" t="n">
-        <v>128.462</v>
+        <v>128.129</v>
       </c>
       <c r="D49" t="n">
-        <v>65.2179</v>
+        <v>64.9552</v>
       </c>
       <c r="E49" t="n">
-        <v>21.842</v>
+        <v>21.9734</v>
       </c>
       <c r="F49" t="n">
-        <v>40.2234</v>
+        <v>38.9733</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>83.4158</v>
+        <v>83.54179999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>125.748</v>
+        <v>126.403</v>
       </c>
       <c r="D50" t="n">
-        <v>79.13039999999999</v>
+        <v>76.2345</v>
       </c>
       <c r="E50" t="n">
-        <v>21.4537</v>
+        <v>21.3244</v>
       </c>
       <c r="F50" t="n">
-        <v>38.5529</v>
+        <v>38.5654</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>82.5016</v>
+        <v>82.39490000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>127.73</v>
+        <v>121.699</v>
       </c>
       <c r="D51" t="n">
-        <v>75.5827</v>
+        <v>79.9584</v>
       </c>
       <c r="E51" t="n">
-        <v>27.0398</v>
+        <v>27.0704</v>
       </c>
       <c r="F51" t="n">
-        <v>47.799</v>
+        <v>48.0197</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>81.9683</v>
+        <v>82.05329999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>123.676</v>
+        <v>124.932</v>
       </c>
       <c r="D52" t="n">
-        <v>75.9521</v>
+        <v>77.86369999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>26.5398</v>
+        <v>26.5568</v>
       </c>
       <c r="F52" t="n">
-        <v>45.2577</v>
+        <v>46.025</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>90.12569999999999</v>
+        <v>90.124</v>
       </c>
       <c r="C53" t="n">
-        <v>135.573</v>
+        <v>139.221</v>
       </c>
       <c r="D53" t="n">
-        <v>68.2719</v>
+        <v>77.3019</v>
       </c>
       <c r="E53" t="n">
-        <v>26.213</v>
+        <v>26.1946</v>
       </c>
       <c r="F53" t="n">
-        <v>44.8686</v>
+        <v>45.6077</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>89.40900000000001</v>
+        <v>89.5629</v>
       </c>
       <c r="C54" t="n">
-        <v>135.836</v>
+        <v>134.988</v>
       </c>
       <c r="D54" t="n">
-        <v>76.6217</v>
+        <v>75.6152</v>
       </c>
       <c r="E54" t="n">
-        <v>25.5564</v>
+        <v>25.5938</v>
       </c>
       <c r="F54" t="n">
-        <v>43.4777</v>
+        <v>43.661</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>89.07340000000001</v>
+        <v>89.0459</v>
       </c>
       <c r="C55" t="n">
-        <v>126.341</v>
+        <v>126.543</v>
       </c>
       <c r="D55" t="n">
-        <v>80.62649999999999</v>
+        <v>80.6202</v>
       </c>
       <c r="E55" t="n">
-        <v>25.1806</v>
+        <v>25.1242</v>
       </c>
       <c r="F55" t="n">
-        <v>42.9038</v>
+        <v>42.8412</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>88.499</v>
+        <v>88.5089</v>
       </c>
       <c r="C56" t="n">
-        <v>125.893</v>
+        <v>146.415</v>
       </c>
       <c r="D56" t="n">
-        <v>78.9586</v>
+        <v>76.1176</v>
       </c>
       <c r="E56" t="n">
-        <v>24.7153</v>
+        <v>24.7479</v>
       </c>
       <c r="F56" t="n">
-        <v>44.0015</v>
+        <v>42.679</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>87.8434</v>
+        <v>87.624</v>
       </c>
       <c r="C57" t="n">
-        <v>137.784</v>
+        <v>137.818</v>
       </c>
       <c r="D57" t="n">
-        <v>74.8477</v>
+        <v>82.1277</v>
       </c>
       <c r="E57" t="n">
-        <v>24.3584</v>
+        <v>24.2945</v>
       </c>
       <c r="F57" t="n">
-        <v>44.2817</v>
+        <v>42.9925</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>87.3009</v>
+        <v>87.34220000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>136.953</v>
+        <v>131.821</v>
       </c>
       <c r="D58" t="n">
-        <v>72.30719999999999</v>
+        <v>76.6545</v>
       </c>
       <c r="E58" t="n">
-        <v>23.9072</v>
+        <v>23.9473</v>
       </c>
       <c r="F58" t="n">
-        <v>42.1978</v>
+        <v>42.5462</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>87.0031</v>
+        <v>87.26179999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>136.358</v>
+        <v>135.653</v>
       </c>
       <c r="D59" t="n">
-        <v>65.2599</v>
+        <v>66.4606</v>
       </c>
       <c r="E59" t="n">
-        <v>23.5829</v>
+        <v>23.5623</v>
       </c>
       <c r="F59" t="n">
-        <v>41.2424</v>
+        <v>41.3588</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>86.12</v>
+        <v>86.47620000000001</v>
       </c>
       <c r="C60" t="n">
-        <v>136.478</v>
+        <v>134.874</v>
       </c>
       <c r="D60" t="n">
-        <v>80.2997</v>
+        <v>82.18040000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>23.1611</v>
+        <v>23.1337</v>
       </c>
       <c r="F60" t="n">
-        <v>40.7334</v>
+        <v>40.6969</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>85.3437</v>
+        <v>85.49420000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>136.536</v>
+        <v>133.905</v>
       </c>
       <c r="D61" t="n">
-        <v>76.07089999999999</v>
+        <v>76.97539999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>22.7539</v>
+        <v>22.7866</v>
       </c>
       <c r="F61" t="n">
-        <v>40.4844</v>
+        <v>40.2848</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>85.0873</v>
+        <v>85.1438</v>
       </c>
       <c r="C62" t="n">
-        <v>137.295</v>
+        <v>136.939</v>
       </c>
       <c r="D62" t="n">
-        <v>68.91889999999999</v>
+        <v>71.0813</v>
       </c>
       <c r="E62" t="n">
-        <v>22.3707</v>
+        <v>22.346</v>
       </c>
       <c r="F62" t="n">
-        <v>43.791</v>
+        <v>40.6022</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>84.11020000000001</v>
+        <v>84.25060000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>122.255</v>
+        <v>122.321</v>
       </c>
       <c r="D63" t="n">
-        <v>74.9157</v>
+        <v>73.0179</v>
       </c>
       <c r="E63" t="n">
-        <v>21.9636</v>
+        <v>21.9811</v>
       </c>
       <c r="F63" t="n">
-        <v>40.9145</v>
+        <v>39.4431</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>83.6498</v>
+        <v>83.58459999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>136.3</v>
+        <v>139.258</v>
       </c>
       <c r="D64" t="n">
-        <v>97.29430000000001</v>
+        <v>99.4923</v>
       </c>
       <c r="E64" t="n">
-        <v>21.5138</v>
+        <v>21.5575</v>
       </c>
       <c r="F64" t="n">
-        <v>38.9271</v>
+        <v>38.9274</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>82.86490000000001</v>
+        <v>82.8175</v>
       </c>
       <c r="C65" t="n">
-        <v>136.879</v>
+        <v>136.064</v>
       </c>
       <c r="D65" t="n">
-        <v>90.8321</v>
+        <v>92.08110000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>21.137</v>
+        <v>21.1179</v>
       </c>
       <c r="F65" t="n">
-        <v>38.3948</v>
+        <v>39.305</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>81.7594</v>
+        <v>81.8475</v>
       </c>
       <c r="C66" t="n">
-        <v>135.663</v>
+        <v>135.878</v>
       </c>
       <c r="D66" t="n">
-        <v>91.54389999999999</v>
+        <v>86.8779</v>
       </c>
       <c r="E66" t="n">
-        <v>27.1752</v>
+        <v>27.151</v>
       </c>
       <c r="F66" t="n">
-        <v>44.8036</v>
+        <v>44.855</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>90.1575</v>
+        <v>90.371</v>
       </c>
       <c r="C67" t="n">
-        <v>142.292</v>
+        <v>148.186</v>
       </c>
       <c r="D67" t="n">
-        <v>82.28319999999999</v>
+        <v>86.7604</v>
       </c>
       <c r="E67" t="n">
-        <v>26.5259</v>
+        <v>26.6986</v>
       </c>
       <c r="F67" t="n">
-        <v>44.9217</v>
+        <v>46.7829</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>89.7667</v>
+        <v>89.64749999999999</v>
       </c>
       <c r="C68" t="n">
-        <v>138.345</v>
+        <v>143.805</v>
       </c>
       <c r="D68" t="n">
-        <v>88.2938</v>
+        <v>91.6212</v>
       </c>
       <c r="E68" t="n">
-        <v>26.1123</v>
+        <v>26.0943</v>
       </c>
       <c r="F68" t="n">
-        <v>43.8468</v>
+        <v>43.9907</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>89.0951</v>
+        <v>89.1223</v>
       </c>
       <c r="C69" t="n">
-        <v>144.678</v>
+        <v>142.834</v>
       </c>
       <c r="D69" t="n">
-        <v>89.8746</v>
+        <v>88.4075</v>
       </c>
       <c r="E69" t="n">
-        <v>25.5324</v>
+        <v>25.6881</v>
       </c>
       <c r="F69" t="n">
-        <v>43.3335</v>
+        <v>43.3307</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>88.8523</v>
+        <v>88.9764</v>
       </c>
       <c r="C70" t="n">
-        <v>144.303</v>
+        <v>141.34</v>
       </c>
       <c r="D70" t="n">
-        <v>87.1807</v>
+        <v>89.38290000000001</v>
       </c>
       <c r="E70" t="n">
-        <v>25.1612</v>
+        <v>25.093</v>
       </c>
       <c r="F70" t="n">
-        <v>46.8068</v>
+        <v>45.6041</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>88.26260000000001</v>
+        <v>88.22920000000001</v>
       </c>
       <c r="C71" t="n">
-        <v>141.905</v>
+        <v>143.641</v>
       </c>
       <c r="D71" t="n">
-        <v>72.735</v>
+        <v>77.6499</v>
       </c>
       <c r="E71" t="n">
-        <v>24.5568</v>
+        <v>24.6313</v>
       </c>
       <c r="F71" t="n">
-        <v>43.5162</v>
+        <v>42.7709</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>87.9438</v>
+        <v>87.6691</v>
       </c>
       <c r="C72" t="n">
-        <v>125.174</v>
+        <v>125.544</v>
       </c>
       <c r="D72" t="n">
-        <v>71.8034</v>
+        <v>73.7176</v>
       </c>
       <c r="E72" t="n">
-        <v>24.0501</v>
+        <v>24.0692</v>
       </c>
       <c r="F72" t="n">
-        <v>42.6208</v>
+        <v>41.8683</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>86.8326</v>
+        <v>86.9139</v>
       </c>
       <c r="C73" t="n">
-        <v>130.685</v>
+        <v>128.635</v>
       </c>
       <c r="D73" t="n">
-        <v>88.5489</v>
+        <v>91.2762</v>
       </c>
       <c r="E73" t="n">
-        <v>23.6565</v>
+        <v>23.7351</v>
       </c>
       <c r="F73" t="n">
-        <v>41.6165</v>
+        <v>41.7622</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>86.3566</v>
+        <v>86.37860000000001</v>
       </c>
       <c r="C74" t="n">
-        <v>148.232</v>
+        <v>155.751</v>
       </c>
       <c r="D74" t="n">
-        <v>92.7149</v>
+        <v>90.6705</v>
       </c>
       <c r="E74" t="n">
-        <v>23.2895</v>
+        <v>23.2755</v>
       </c>
       <c r="F74" t="n">
-        <v>41.0084</v>
+        <v>42.0504</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>85.6683</v>
+        <v>85.7289</v>
       </c>
       <c r="C75" t="n">
-        <v>146.184</v>
+        <v>150.607</v>
       </c>
       <c r="D75" t="n">
-        <v>90.066</v>
+        <v>96.3424</v>
       </c>
       <c r="E75" t="n">
-        <v>22.8484</v>
+        <v>22.9205</v>
       </c>
       <c r="F75" t="n">
-        <v>40.4308</v>
+        <v>40.3715</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>85.122</v>
+        <v>85.1202</v>
       </c>
       <c r="C76" t="n">
-        <v>143.606</v>
+        <v>148.501</v>
       </c>
       <c r="D76" t="n">
-        <v>81.3954</v>
+        <v>83.5347</v>
       </c>
       <c r="E76" t="n">
-        <v>22.4521</v>
+        <v>22.4579</v>
       </c>
       <c r="F76" t="n">
-        <v>41.2877</v>
+        <v>40.0112</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>84.45959999999999</v>
+        <v>84.5125</v>
       </c>
       <c r="C77" t="n">
-        <v>150.21</v>
+        <v>137.985</v>
       </c>
       <c r="D77" t="n">
-        <v>77.7308</v>
+        <v>77.1053</v>
       </c>
       <c r="E77" t="n">
-        <v>22.0833</v>
+        <v>22.0784</v>
       </c>
       <c r="F77" t="n">
-        <v>39.662</v>
+        <v>39.4833</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>84.0441</v>
+        <v>83.6848</v>
       </c>
       <c r="C78" t="n">
-        <v>139.42</v>
+        <v>141.501</v>
       </c>
       <c r="D78" t="n">
-        <v>102.62</v>
+        <v>100.817</v>
       </c>
       <c r="E78" t="n">
-        <v>21.6399</v>
+        <v>21.6465</v>
       </c>
       <c r="F78" t="n">
-        <v>39.1258</v>
+        <v>38.9881</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>82.8419</v>
+        <v>82.6412</v>
       </c>
       <c r="C79" t="n">
-        <v>141.493</v>
+        <v>143.263</v>
       </c>
       <c r="D79" t="n">
-        <v>95.7379</v>
+        <v>91.7542</v>
       </c>
       <c r="E79" t="n">
-        <v>21.2405</v>
+        <v>21.2253</v>
       </c>
       <c r="F79" t="n">
-        <v>38.4773</v>
+        <v>38.4963</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>82.00449999999999</v>
+        <v>81.7777</v>
       </c>
       <c r="C80" t="n">
-        <v>144.52</v>
+        <v>146.363</v>
       </c>
       <c r="D80" t="n">
-        <v>97.4161</v>
+        <v>93.9234</v>
       </c>
       <c r="E80" t="n">
-        <v>26.914</v>
+        <v>26.9659</v>
       </c>
       <c r="F80" t="n">
-        <v>44.8397</v>
+        <v>44.8534</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>90.3556</v>
+        <v>90.197</v>
       </c>
       <c r="C81" t="n">
-        <v>150.398</v>
+        <v>141.951</v>
       </c>
       <c r="D81" t="n">
-        <v>97.0324</v>
+        <v>95.5145</v>
       </c>
       <c r="E81" t="n">
-        <v>26.3139</v>
+        <v>26.4516</v>
       </c>
       <c r="F81" t="n">
-        <v>44.1629</v>
+        <v>44.1639</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>90.2427</v>
+        <v>90.15860000000001</v>
       </c>
       <c r="C82" t="n">
-        <v>146.638</v>
+        <v>148.912</v>
       </c>
       <c r="D82" t="n">
-        <v>95.5917</v>
+        <v>94.7948</v>
       </c>
       <c r="E82" t="n">
-        <v>25.8865</v>
+        <v>25.8416</v>
       </c>
       <c r="F82" t="n">
-        <v>43.7278</v>
+        <v>43.6774</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>89.7773</v>
+        <v>89.6613</v>
       </c>
       <c r="C83" t="n">
-        <v>149.57</v>
+        <v>147.305</v>
       </c>
       <c r="D83" t="n">
-        <v>82.8475</v>
+        <v>87.1324</v>
       </c>
       <c r="E83" t="n">
-        <v>25.4566</v>
+        <v>25.4372</v>
       </c>
       <c r="F83" t="n">
-        <v>43.7031</v>
+        <v>43.2066</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>89.6623</v>
+        <v>89.3879</v>
       </c>
       <c r="C84" t="n">
-        <v>150.571</v>
+        <v>150.304</v>
       </c>
       <c r="D84" t="n">
-        <v>81.4049</v>
+        <v>82.26900000000001</v>
       </c>
       <c r="E84" t="n">
-        <v>24.9149</v>
+        <v>24.9534</v>
       </c>
       <c r="F84" t="n">
-        <v>42.6893</v>
+        <v>42.9045</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>88.5539</v>
+        <v>88.4742</v>
       </c>
       <c r="C85" t="n">
-        <v>149.282</v>
+        <v>148.868</v>
       </c>
       <c r="D85" t="n">
-        <v>79.8419</v>
+        <v>79.7817</v>
       </c>
       <c r="E85" t="n">
-        <v>24.5379</v>
+        <v>24.5218</v>
       </c>
       <c r="F85" t="n">
-        <v>42.3054</v>
+        <v>42.3905</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>87.6892</v>
+        <v>87.7195</v>
       </c>
       <c r="C86" t="n">
-        <v>150.104</v>
+        <v>148.44</v>
       </c>
       <c r="D86" t="n">
-        <v>99.50530000000001</v>
+        <v>96.3809</v>
       </c>
       <c r="E86" t="n">
-        <v>24.2673</v>
+        <v>24.2085</v>
       </c>
       <c r="F86" t="n">
-        <v>42.3965</v>
+        <v>42.0346</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>87.10250000000001</v>
+        <v>86.9098</v>
       </c>
       <c r="C87" t="n">
-        <v>149.921</v>
+        <v>152.161</v>
       </c>
       <c r="D87" t="n">
-        <v>105.674</v>
+        <v>102.868</v>
       </c>
       <c r="E87" t="n">
-        <v>23.8039</v>
+        <v>23.8128</v>
       </c>
       <c r="F87" t="n">
-        <v>41.5768</v>
+        <v>41.5745</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>86.6151</v>
+        <v>86.5198</v>
       </c>
       <c r="C88" t="n">
-        <v>154.983</v>
+        <v>148.642</v>
       </c>
       <c r="D88" t="n">
-        <v>101.447</v>
+        <v>102.825</v>
       </c>
       <c r="E88" t="n">
-        <v>23.4246</v>
+        <v>23.4226</v>
       </c>
       <c r="F88" t="n">
-        <v>40.7935</v>
+        <v>40.8337</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>85.8805</v>
+        <v>85.8348</v>
       </c>
       <c r="C89" t="n">
-        <v>148.565</v>
+        <v>147.693</v>
       </c>
       <c r="D89" t="n">
-        <v>92.2749</v>
+        <v>84.8818</v>
       </c>
       <c r="E89" t="n">
-        <v>22.9928</v>
+        <v>22.9971</v>
       </c>
       <c r="F89" t="n">
-        <v>40.427</v>
+        <v>40.3692</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>85.2269</v>
+        <v>85.1534</v>
       </c>
       <c r="C90" t="n">
-        <v>121.599</v>
+        <v>120.455</v>
       </c>
       <c r="D90" t="n">
-        <v>86.13330000000001</v>
+        <v>83.09269999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>22.6016</v>
+        <v>22.5949</v>
       </c>
       <c r="F90" t="n">
-        <v>40.1272</v>
+        <v>40.166</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>84.76990000000001</v>
+        <v>84.47669999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>123.737</v>
+        <v>121.893</v>
       </c>
       <c r="D91" t="n">
-        <v>86.99469999999999</v>
+        <v>83.7525</v>
       </c>
       <c r="E91" t="n">
-        <v>22.2475</v>
+        <v>22.2734</v>
       </c>
       <c r="F91" t="n">
-        <v>39.8855</v>
+        <v>39.7111</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>84.0133</v>
+        <v>83.8197</v>
       </c>
       <c r="C92" t="n">
-        <v>119.732</v>
+        <v>119.424</v>
       </c>
       <c r="D92" t="n">
-        <v>95.7773</v>
+        <v>94.61969999999999</v>
       </c>
       <c r="E92" t="n">
-        <v>21.8485</v>
+        <v>21.8343</v>
       </c>
       <c r="F92" t="n">
-        <v>39.1291</v>
+        <v>39.0457</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>83.21639999999999</v>
+        <v>83.01519999999999</v>
       </c>
       <c r="C93" t="n">
-        <v>118.624</v>
+        <v>128.286</v>
       </c>
       <c r="D93" t="n">
-        <v>90.40949999999999</v>
+        <v>97.7456</v>
       </c>
       <c r="E93" t="n">
-        <v>21.4256</v>
+        <v>21.4827</v>
       </c>
       <c r="F93" t="n">
-        <v>38.6287</v>
+        <v>38.5367</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>82.3335</v>
+        <v>82.22669999999999</v>
       </c>
       <c r="C94" t="n">
-        <v>149.531</v>
+        <v>153.773</v>
       </c>
       <c r="D94" t="n">
-        <v>92.12649999999999</v>
+        <v>91.6391</v>
       </c>
       <c r="E94" t="n">
-        <v>27.0803</v>
+        <v>27.0325</v>
       </c>
       <c r="F94" t="n">
-        <v>44.6572</v>
+        <v>44.8248</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>90.80419999999999</v>
+        <v>90.7961</v>
       </c>
       <c r="C95" t="n">
-        <v>173.968</v>
+        <v>169.438</v>
       </c>
       <c r="D95" t="n">
-        <v>88.40940000000001</v>
+        <v>86.31950000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>26.6066</v>
+        <v>26.3993</v>
       </c>
       <c r="F95" t="n">
-        <v>44.2164</v>
+        <v>44.4142</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>90.1097</v>
+        <v>90.13160000000001</v>
       </c>
       <c r="C96" t="n">
-        <v>141.379</v>
+        <v>140.282</v>
       </c>
       <c r="D96" t="n">
-        <v>88.7017</v>
+        <v>90.9645</v>
       </c>
       <c r="E96" t="n">
-        <v>26.029</v>
+        <v>25.9923</v>
       </c>
       <c r="F96" t="n">
-        <v>43.8045</v>
+        <v>43.7273</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>89.616</v>
+        <v>89.5685</v>
       </c>
       <c r="C97" t="n">
-        <v>159.13</v>
+        <v>157.024</v>
       </c>
       <c r="D97" t="n">
-        <v>81.4717</v>
+        <v>81.82689999999999</v>
       </c>
       <c r="E97" t="n">
-        <v>25.4879</v>
+        <v>25.4986</v>
       </c>
       <c r="F97" t="n">
-        <v>43.1965</v>
+        <v>43.2864</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>88.9842</v>
+        <v>89.0509</v>
       </c>
       <c r="C98" t="n">
-        <v>157.796</v>
+        <v>153.417</v>
       </c>
       <c r="D98" t="n">
-        <v>80.5185</v>
+        <v>79.4198</v>
       </c>
       <c r="E98" t="n">
-        <v>25.0889</v>
+        <v>25.0596</v>
       </c>
       <c r="F98" t="n">
-        <v>42.6532</v>
+        <v>42.6976</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>88.2175</v>
+        <v>88.3877</v>
       </c>
       <c r="C99" t="n">
-        <v>152.964</v>
+        <v>152.256</v>
       </c>
       <c r="D99" t="n">
-        <v>83.7385</v>
+        <v>84.30029999999999</v>
       </c>
       <c r="E99" t="n">
-        <v>24.6615</v>
+        <v>24.7165</v>
       </c>
       <c r="F99" t="n">
-        <v>42.2509</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>87.74169999999999</v>
+        <v>87.5171</v>
       </c>
       <c r="C100" t="n">
-        <v>158.112</v>
+        <v>153.399</v>
       </c>
       <c r="D100" t="n">
-        <v>77.7394</v>
+        <v>77.0098</v>
       </c>
       <c r="E100" t="n">
-        <v>24.3721</v>
+        <v>24.273</v>
       </c>
       <c r="F100" t="n">
-        <v>41.7406</v>
+        <v>41.6664</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>86.6797</v>
+        <v>86.5752</v>
       </c>
       <c r="C101" t="n">
-        <v>165.894</v>
+        <v>146.584</v>
       </c>
       <c r="D101" t="n">
-        <v>90.5117</v>
+        <v>88.24509999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>23.9506</v>
+        <v>23.8285</v>
       </c>
       <c r="F101" t="n">
-        <v>41.279</v>
+        <v>41.2879</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>86.35550000000001</v>
+        <v>85.98180000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>152.28</v>
+        <v>154.063</v>
       </c>
       <c r="D102" t="n">
-        <v>78.4218</v>
+        <v>78.2552</v>
       </c>
       <c r="E102" t="n">
-        <v>23.5314</v>
+        <v>23.5008</v>
       </c>
       <c r="F102" t="n">
-        <v>40.9598</v>
+        <v>40.8976</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>85.6493</v>
+        <v>84.9504</v>
       </c>
       <c r="C103" t="n">
-        <v>152.454</v>
+        <v>152.009</v>
       </c>
       <c r="D103" t="n">
-        <v>79.7124</v>
+        <v>80.7578</v>
       </c>
       <c r="E103" t="n">
-        <v>23.1437</v>
+        <v>23.0844</v>
       </c>
       <c r="F103" t="n">
-        <v>40.3277</v>
+        <v>40.3124</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>84.6767</v>
+        <v>84.8942</v>
       </c>
       <c r="C104" t="n">
-        <v>157.371</v>
+        <v>151.402</v>
       </c>
       <c r="D104" t="n">
-        <v>72.93300000000001</v>
+        <v>74.0283</v>
       </c>
       <c r="E104" t="n">
-        <v>22.7385</v>
+        <v>22.7961</v>
       </c>
       <c r="F104" t="n">
-        <v>40.1315</v>
+        <v>40.1537</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>84.614</v>
+        <v>84.4619</v>
       </c>
       <c r="C105" t="n">
-        <v>152.247</v>
+        <v>152.178</v>
       </c>
       <c r="D105" t="n">
-        <v>68.2619</v>
+        <v>73.1789</v>
       </c>
       <c r="E105" t="n">
-        <v>22.4032</v>
+        <v>22.4204</v>
       </c>
       <c r="F105" t="n">
-        <v>39.4638</v>
+        <v>39.5601</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>83.9824</v>
+        <v>83.7748</v>
       </c>
       <c r="C106" t="n">
-        <v>163.808</v>
+        <v>153.269</v>
       </c>
       <c r="D106" t="n">
-        <v>81.34350000000001</v>
+        <v>79.4526</v>
       </c>
       <c r="E106" t="n">
-        <v>22.0174</v>
+        <v>22.0185</v>
       </c>
       <c r="F106" t="n">
-        <v>39.0322</v>
+        <v>39.0835</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>83.21259999999999</v>
+        <v>83.0956</v>
       </c>
       <c r="C107" t="n">
-        <v>152.218</v>
+        <v>149.097</v>
       </c>
       <c r="D107" t="n">
-        <v>85.6456</v>
+        <v>85.5385</v>
       </c>
       <c r="E107" t="n">
-        <v>21.629</v>
+        <v>21.6054</v>
       </c>
       <c r="F107" t="n">
-        <v>38.6195</v>
+        <v>38.5652</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>82.30759999999999</v>
+        <v>82.0741</v>
       </c>
       <c r="C108" t="n">
-        <v>156.177</v>
+        <v>151.557</v>
       </c>
       <c r="D108" t="n">
-        <v>90.59399999999999</v>
+        <v>88.4406</v>
       </c>
       <c r="E108" t="n">
-        <v>27.2867</v>
+        <v>27.2528</v>
       </c>
       <c r="F108" t="n">
-        <v>44.776</v>
+        <v>44.9419</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>81.34139999999999</v>
+        <v>81.2706</v>
       </c>
       <c r="C109" t="n">
-        <v>161.106</v>
+        <v>164.988</v>
       </c>
       <c r="D109" t="n">
-        <v>85.5132</v>
+        <v>85.7627</v>
       </c>
       <c r="E109" t="n">
-        <v>26.7523</v>
+        <v>26.7464</v>
       </c>
       <c r="F109" t="n">
-        <v>44.3164</v>
+        <v>44.3592</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>89.76439999999999</v>
+        <v>89.7055</v>
       </c>
       <c r="C110" t="n">
-        <v>156.963</v>
+        <v>151.924</v>
       </c>
       <c r="D110" t="n">
-        <v>91.1567</v>
+        <v>83.0316</v>
       </c>
       <c r="E110" t="n">
-        <v>26.2635</v>
+        <v>26.1414</v>
       </c>
       <c r="F110" t="n">
-        <v>43.761</v>
+        <v>43.7529</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>89.8926</v>
+        <v>89.7324</v>
       </c>
       <c r="C111" t="n">
-        <v>162.597</v>
+        <v>159.224</v>
       </c>
       <c r="D111" t="n">
-        <v>76.9933</v>
+        <v>77.18559999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>25.7675</v>
+        <v>25.7151</v>
       </c>
       <c r="F111" t="n">
-        <v>43.5208</v>
+        <v>43.5965</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>88.6164</v>
+        <v>89.2491</v>
       </c>
       <c r="C112" t="n">
-        <v>172.036</v>
+        <v>176.552</v>
       </c>
       <c r="D112" t="n">
-        <v>82.2312</v>
+        <v>81.95569999999999</v>
       </c>
       <c r="E112" t="n">
-        <v>25.3512</v>
+        <v>25.3395</v>
       </c>
       <c r="F112" t="n">
-        <v>43.186</v>
+        <v>43.1659</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>88.559</v>
+        <v>88.6322</v>
       </c>
       <c r="C113" t="n">
-        <v>189.407</v>
+        <v>183.594</v>
       </c>
       <c r="D113" t="n">
-        <v>73.5804</v>
+        <v>74.0658</v>
       </c>
       <c r="E113" t="n">
-        <v>24.8787</v>
+        <v>24.8925</v>
       </c>
       <c r="F113" t="n">
-        <v>42.6892</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>87.9796</v>
+        <v>87.91249999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>179.471</v>
+        <v>186.454</v>
       </c>
       <c r="D114" t="n">
-        <v>74.742</v>
+        <v>79.61060000000001</v>
       </c>
       <c r="E114" t="n">
-        <v>24.4662</v>
+        <v>24.289</v>
       </c>
       <c r="F114" t="n">
-        <v>42.0877</v>
+        <v>42.2469</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>87.42319999999999</v>
+        <v>87.30800000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>187.93</v>
+        <v>179.478</v>
       </c>
       <c r="D115" t="n">
-        <v>73.7259</v>
+        <v>71.39060000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>23.987</v>
+        <v>23.9793</v>
       </c>
       <c r="F115" t="n">
-        <v>41.4585</v>
+        <v>41.4485</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>87.30629999999999</v>
+        <v>86.8698</v>
       </c>
       <c r="C116" t="n">
-        <v>183.209</v>
+        <v>187.192</v>
       </c>
       <c r="D116" t="n">
-        <v>69.3665</v>
+        <v>70.4324</v>
       </c>
       <c r="E116" t="n">
-        <v>23.5784</v>
+        <v>23.5797</v>
       </c>
       <c r="F116" t="n">
-        <v>41.0821</v>
+        <v>41.2572</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>86.155</v>
+        <v>85.9357</v>
       </c>
       <c r="C117" t="n">
-        <v>203.88</v>
+        <v>193.245</v>
       </c>
       <c r="D117" t="n">
-        <v>69.2266</v>
+        <v>69.46899999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>23.2131</v>
+        <v>23.1649</v>
       </c>
       <c r="F117" t="n">
-        <v>40.6126</v>
+        <v>40.8158</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>85.5971</v>
+        <v>85.53440000000001</v>
       </c>
       <c r="C118" t="n">
-        <v>191.594</v>
+        <v>191.308</v>
       </c>
       <c r="D118" t="n">
-        <v>66.6557</v>
+        <v>66.83620000000001</v>
       </c>
       <c r="E118" t="n">
-        <v>22.7606</v>
+        <v>22.7589</v>
       </c>
       <c r="F118" t="n">
-        <v>40.1325</v>
+        <v>40.3202</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>84.8985</v>
+        <v>84.9385</v>
       </c>
       <c r="C119" t="n">
-        <v>180.542</v>
+        <v>180.347</v>
       </c>
       <c r="D119" t="n">
-        <v>66.21769999999999</v>
+        <v>66.1121</v>
       </c>
       <c r="E119" t="n">
-        <v>22.4004</v>
+        <v>22.4135</v>
       </c>
       <c r="F119" t="n">
-        <v>39.7898</v>
+        <v>40.0799</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>84.051</v>
+        <v>83.98779999999999</v>
       </c>
       <c r="C120" t="n">
-        <v>189.317</v>
+        <v>189.911</v>
       </c>
       <c r="D120" t="n">
-        <v>64.7029</v>
+        <v>64.75660000000001</v>
       </c>
       <c r="E120" t="n">
-        <v>22.0286</v>
+        <v>22.0514</v>
       </c>
       <c r="F120" t="n">
-        <v>39.2677</v>
+        <v>39.2166</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>83.2814</v>
+        <v>83.2743</v>
       </c>
       <c r="C121" t="n">
-        <v>192.873</v>
+        <v>196.095</v>
       </c>
       <c r="D121" t="n">
-        <v>86.3951</v>
+        <v>86.63679999999999</v>
       </c>
       <c r="E121" t="n">
-        <v>21.6688</v>
+        <v>21.6643</v>
       </c>
       <c r="F121" t="n">
-        <v>38.7577</v>
+        <v>38.6943</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>82.4823</v>
+        <v>82.4602</v>
       </c>
       <c r="C122" t="n">
-        <v>201.227</v>
+        <v>201.362</v>
       </c>
       <c r="D122" t="n">
-        <v>85.6178</v>
+        <v>84.57640000000001</v>
       </c>
       <c r="E122" t="n">
-        <v>21.2648</v>
+        <v>21.2689</v>
       </c>
       <c r="F122" t="n">
-        <v>38.219</v>
+        <v>38.2489</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>81.5239</v>
+        <v>81.4397</v>
       </c>
       <c r="C123" t="n">
-        <v>192.707</v>
+        <v>187.974</v>
       </c>
       <c r="D123" t="n">
-        <v>133.854</v>
+        <v>126.131</v>
       </c>
       <c r="E123" t="n">
-        <v>26.6973</v>
+        <v>26.7574</v>
       </c>
       <c r="F123" t="n">
-        <v>44.4254</v>
+        <v>44.5776</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>90.6707</v>
+        <v>90.7123</v>
       </c>
       <c r="C124" t="n">
-        <v>208.005</v>
+        <v>210.101</v>
       </c>
       <c r="D124" t="n">
-        <v>80.4301</v>
+        <v>80.63849999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>26.2105</v>
+        <v>26.2494</v>
       </c>
       <c r="F124" t="n">
-        <v>43.8924</v>
+        <v>43.9596</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>89.9402</v>
+        <v>89.9134</v>
       </c>
       <c r="C125" t="n">
-        <v>210.413</v>
+        <v>210.13</v>
       </c>
       <c r="D125" t="n">
-        <v>78.883</v>
+        <v>78.7608</v>
       </c>
       <c r="E125" t="n">
-        <v>25.8792</v>
+        <v>25.7966</v>
       </c>
       <c r="F125" t="n">
-        <v>43.3435</v>
+        <v>43.5728</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>89.4087</v>
+        <v>89.4795</v>
       </c>
       <c r="C126" t="n">
-        <v>210.451</v>
+        <v>210.067</v>
       </c>
       <c r="D126" t="n">
-        <v>78.7384</v>
+        <v>78.35550000000001</v>
       </c>
       <c r="E126" t="n">
-        <v>25.3429</v>
+        <v>25.4183</v>
       </c>
       <c r="F126" t="n">
-        <v>42.9297</v>
+        <v>42.8631</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>88.7427</v>
+        <v>88.0322</v>
       </c>
       <c r="C127" t="n">
-        <v>213.202</v>
+        <v>213.415</v>
       </c>
       <c r="D127" t="n">
-        <v>75.6503</v>
+        <v>75.53360000000001</v>
       </c>
       <c r="E127" t="n">
-        <v>24.9034</v>
+        <v>24.9846</v>
       </c>
       <c r="F127" t="n">
-        <v>42.4049</v>
+        <v>42.391</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>87.9119</v>
+        <v>87.9453</v>
       </c>
       <c r="C128" t="n">
-        <v>213.543</v>
+        <v>212.017</v>
       </c>
       <c r="D128" t="n">
-        <v>77.4041</v>
+        <v>75.1481</v>
       </c>
       <c r="E128" t="n">
-        <v>24.4744</v>
+        <v>24.4592</v>
       </c>
       <c r="F128" t="n">
-        <v>41.9354</v>
+        <v>42.1332</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>87.2552</v>
+        <v>87.32859999999999</v>
       </c>
       <c r="C129" t="n">
-        <v>214.352</v>
+        <v>217.503</v>
       </c>
       <c r="D129" t="n">
-        <v>87.7606</v>
+        <v>86.07769999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>24.0757</v>
+        <v>24.121</v>
       </c>
       <c r="F129" t="n">
-        <v>41.6562</v>
+        <v>41.6138</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>86.63200000000001</v>
+        <v>86.76130000000001</v>
       </c>
       <c r="C130" t="n">
-        <v>195.306</v>
+        <v>196.618</v>
       </c>
       <c r="D130" t="n">
-        <v>91.8883</v>
+        <v>106.662</v>
       </c>
       <c r="E130" t="n">
-        <v>23.7045</v>
+        <v>23.6896</v>
       </c>
       <c r="F130" t="n">
-        <v>41.2005</v>
+        <v>41.3547</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>85.8413</v>
+        <v>85.7696</v>
       </c>
       <c r="C131" t="n">
-        <v>192.489</v>
+        <v>192.891</v>
       </c>
       <c r="D131" t="n">
-        <v>93.815</v>
+        <v>94.932</v>
       </c>
       <c r="E131" t="n">
-        <v>23.2839</v>
+        <v>23.297</v>
       </c>
       <c r="F131" t="n">
-        <v>40.7328</v>
+        <v>40.7494</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>85.2723</v>
+        <v>85.06480000000001</v>
       </c>
       <c r="C132" t="n">
-        <v>189.033</v>
+        <v>194.817</v>
       </c>
       <c r="D132" t="n">
-        <v>83.4229</v>
+        <v>87.90819999999999</v>
       </c>
       <c r="E132" t="n">
-        <v>22.927</v>
+        <v>22.8803</v>
       </c>
       <c r="F132" t="n">
-        <v>40.1842</v>
+        <v>40.1539</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>84.7192</v>
+        <v>84.89319999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>191.832</v>
+        <v>190.555</v>
       </c>
       <c r="D133" t="n">
-        <v>82.4901</v>
+        <v>81.0639</v>
       </c>
       <c r="E133" t="n">
-        <v>22.5203</v>
+        <v>22.5417</v>
       </c>
       <c r="F133" t="n">
-        <v>39.6642</v>
+        <v>39.8233</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>84.41160000000001</v>
+        <v>83.8736</v>
       </c>
       <c r="C134" t="n">
-        <v>191.117</v>
+        <v>193.333</v>
       </c>
       <c r="D134" t="n">
-        <v>86.086</v>
+        <v>102.089</v>
       </c>
       <c r="E134" t="n">
-        <v>22.1071</v>
+        <v>22.1249</v>
       </c>
       <c r="F134" t="n">
-        <v>39.3302</v>
+        <v>39.4138</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>83.3746</v>
+        <v>83.4413</v>
       </c>
       <c r="C135" t="n">
-        <v>207.828</v>
+        <v>209.018</v>
       </c>
       <c r="D135" t="n">
-        <v>99.3385</v>
+        <v>112.571</v>
       </c>
       <c r="E135" t="n">
-        <v>21.7246</v>
+        <v>21.7256</v>
       </c>
       <c r="F135" t="n">
-        <v>39.0591</v>
+        <v>39.0767</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>82.7321</v>
+        <v>82.6327</v>
       </c>
       <c r="C136" t="n">
-        <v>207.571</v>
+        <v>208.987</v>
       </c>
       <c r="D136" t="n">
-        <v>108.595</v>
+        <v>111.054</v>
       </c>
       <c r="E136" t="n">
-        <v>21.3397</v>
+        <v>21.3104</v>
       </c>
       <c r="F136" t="n">
-        <v>38.3347</v>
+        <v>38.4099</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>81.9909</v>
+        <v>81.91160000000001</v>
       </c>
       <c r="C137" t="n">
-        <v>204.114</v>
+        <v>202.656</v>
       </c>
       <c r="D137" t="n">
-        <v>94.7501</v>
+        <v>109.397</v>
       </c>
       <c r="E137" t="n">
-        <v>26.8522</v>
+        <v>26.8316</v>
       </c>
       <c r="F137" t="n">
-        <v>44.7179</v>
+        <v>44.6651</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>121.972</v>
+        <v>123.028</v>
       </c>
       <c r="C138" t="n">
-        <v>209.156</v>
+        <v>209.11</v>
       </c>
       <c r="D138" t="n">
-        <v>130.42</v>
+        <v>132.506</v>
       </c>
       <c r="E138" t="n">
-        <v>26.3422</v>
+        <v>26.3343</v>
       </c>
       <c r="F138" t="n">
-        <v>44.2901</v>
+        <v>44.3183</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>118.347</v>
+        <v>124.08</v>
       </c>
       <c r="C139" t="n">
-        <v>203.724</v>
+        <v>205.806</v>
       </c>
       <c r="D139" t="n">
-        <v>120.371</v>
+        <v>116.061</v>
       </c>
       <c r="E139" t="n">
-        <v>25.9196</v>
+        <v>25.9302</v>
       </c>
       <c r="F139" t="n">
-        <v>43.6069</v>
+        <v>43.5758</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>115.441</v>
+        <v>114.898</v>
       </c>
       <c r="C140" t="n">
-        <v>203.816</v>
+        <v>202.425</v>
       </c>
       <c r="D140" t="n">
-        <v>100.665</v>
+        <v>97.30759999999999</v>
       </c>
       <c r="E140" t="n">
-        <v>25.4661</v>
+        <v>25.3597</v>
       </c>
       <c r="F140" t="n">
-        <v>43.2305</v>
+        <v>43.2089</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>114.437</v>
+        <v>117.79</v>
       </c>
       <c r="C141" t="n">
-        <v>226.932</v>
+        <v>226.249</v>
       </c>
       <c r="D141" t="n">
-        <v>93.7718</v>
+        <v>92.2657</v>
       </c>
       <c r="E141" t="n">
-        <v>25.0159</v>
+        <v>24.9925</v>
       </c>
       <c r="F141" t="n">
-        <v>42.64</v>
+        <v>42.6643</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>119.074</v>
+        <v>117.269</v>
       </c>
       <c r="C142" t="n">
-        <v>210.736</v>
+        <v>212.022</v>
       </c>
       <c r="D142" t="n">
-        <v>93.77849999999999</v>
+        <v>94.2863</v>
       </c>
       <c r="E142" t="n">
-        <v>24.5904</v>
+        <v>24.6024</v>
       </c>
       <c r="F142" t="n">
-        <v>42.4904</v>
+        <v>42.4586</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>120.056</v>
+        <v>111.201</v>
       </c>
       <c r="C143" t="n">
-        <v>203.499</v>
+        <v>201.793</v>
       </c>
       <c r="D143" t="n">
-        <v>88.28279999999999</v>
+        <v>96.1579</v>
       </c>
       <c r="E143" t="n">
-        <v>24.1671</v>
+        <v>24.1255</v>
       </c>
       <c r="F143" t="n">
-        <v>41.783</v>
+        <v>41.7172</v>
       </c>
     </row>
   </sheetData>
